--- a/docs/Logic Requirements/Ageipelago William Wallace.xlsx
+++ b/docs/Logic Requirements/Ageipelago William Wallace.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5108BDF-AEF7-40DC-B04B-986497EE0687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F72C19-E391-4D99-A4E8-ABDB76E06757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="893" activeTab="7" xr2:uid="{1D996FA3-8E71-4AAB-A721-F834CDA60D66}"/>
+    <workbookView xWindow="-28020" yWindow="1260" windowWidth="27750" windowHeight="13740" tabRatio="893" activeTab="1" xr2:uid="{1D996FA3-8E71-4AAB-A721-F834CDA60D66}"/>
   </bookViews>
   <sheets>
     <sheet name="William Wallace" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="149">
   <si>
     <t>Scenario</t>
   </si>
@@ -732,61 +732,106 @@
     <t>Unavailable</t>
   </si>
   <si>
-    <t>Loom</t>
-  </si>
-  <si>
-    <t>Dock</t>
-  </si>
-  <si>
-    <t>Palisade Gate</t>
-  </si>
-  <si>
-    <t>Fishing Trap</t>
-  </si>
-  <si>
-    <t>Fishing Lines</t>
-  </si>
-  <si>
     <t>Dark - Feudal Age</t>
   </si>
   <si>
-    <t>Fishing Ship</t>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Feudal - Castle Age</t>
+  </si>
+  <si>
+    <t>Feudal - Imperial Age</t>
+  </si>
+  <si>
+    <t>No Castle</t>
+  </si>
+  <si>
+    <t>No Woad Raider</t>
+  </si>
+  <si>
+    <t>No Petard</t>
+  </si>
+  <si>
+    <t>No Stronghold</t>
+  </si>
+  <si>
+    <t>No Dock</t>
+  </si>
+  <si>
+    <t>No Palisade Wall</t>
+  </si>
+  <si>
+    <t>No Palisade Gate</t>
+  </si>
+  <si>
+    <t>No Fishing Trap</t>
+  </si>
+  <si>
+    <t>No Stone Wall</t>
+  </si>
+  <si>
+    <t>No Stone Gate</t>
+  </si>
+  <si>
+    <t>No Trade Cog</t>
+  </si>
+  <si>
+    <t>No Demolition Raft</t>
+  </si>
+  <si>
+    <t>No Hulk</t>
+  </si>
+  <si>
+    <t>No Galley</t>
+  </si>
+  <si>
+    <t>No Fire Galley</t>
+  </si>
+  <si>
+    <t>No Transport Ship</t>
+  </si>
+  <si>
+    <t>No Fishing Ship</t>
+  </si>
+  <si>
+    <t>No Fishing Lines</t>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>Enough Houses</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Galleon</t>
   </si>
   <si>
     <t>Transport Ship</t>
   </si>
   <si>
-    <t>Fire Galley</t>
-  </si>
-  <si>
-    <t>Galley</t>
-  </si>
-  <si>
-    <t>Hulk</t>
-  </si>
-  <si>
-    <t>Demolition Raft</t>
-  </si>
-  <si>
-    <t>Trade Cog</t>
-  </si>
-  <si>
-    <t>Unrestricted</t>
-  </si>
-  <si>
-    <t>Woad Raider</t>
-  </si>
-  <si>
-    <t>Petard</t>
-  </si>
-  <si>
-    <t>Stronghold</t>
-  </si>
-  <si>
-    <t>Feudal - Castle Age</t>
-  </si>
-  <si>
-    <t>Feudal - Imperial Age</t>
+    <t>Paladin</t>
+  </si>
+  <si>
+    <t>Elite Woad Raider</t>
+  </si>
+  <si>
+    <t>William Wallace</t>
   </si>
 </sst>
 </file>
@@ -912,7 +957,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1096,11 +1141,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1224,6 +1302,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1876,6 +1963,7 @@
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="6" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
@@ -1883,11 +1971,11 @@
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:13" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34"/>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -1902,11 +1990,11 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
@@ -1967,7 +2055,7 @@
       <c r="K6" s="25"/>
       <c r="L6" s="25"/>
     </row>
-    <row r="7" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="35"/>
       <c r="C7" s="35"/>
       <c r="D7" s="25"/>
@@ -1976,28 +2064,43 @@
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
     </row>
-    <row r="8" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="25"/>
+    <row r="8" spans="1:13" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>140</v>
+      </c>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
       <c r="K8" s="25"/>
       <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="36"/>
+      <c r="D9" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" s="36"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
       <c r="K9" s="25"/>
       <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="25"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
       <c r="K10" s="25"/>
@@ -2006,25 +2109,28 @@
     <row r="11" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
-      <c r="D11" s="25"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
       <c r="K11" s="25"/>
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="25"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
       <c r="K12" s="25"/>
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="25"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
       <c r="K13" s="25"/>
@@ -2034,7 +2140,8 @@
     <row r="14" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
-      <c r="D14" s="25"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
       <c r="K14" s="25"/>
@@ -2042,9 +2149,10 @@
       <c r="M14" s="26"/>
     </row>
     <row r="15" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="25"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="K15" s="25"/>
@@ -2052,121 +2160,142 @@
       <c r="M15" s="26"/>
     </row>
     <row r="16" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="25"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
       <c r="M16" s="26"/>
     </row>
-    <row r="17" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
       <c r="K17" s="25"/>
       <c r="L17" s="25"/>
       <c r="M17" s="26"/>
     </row>
-    <row r="18" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="K18" s="25"/>
       <c r="L18" s="25"/>
       <c r="M18" s="26"/>
     </row>
-    <row r="19" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
       <c r="K19" s="25"/>
       <c r="L19" s="25"/>
       <c r="M19" s="26"/>
     </row>
-    <row r="20" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="25"/>
       <c r="H20" s="25"/>
       <c r="K20" s="25"/>
       <c r="L20" s="25"/>
       <c r="M20" s="26"/>
     </row>
-    <row r="21" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
       <c r="K21" s="25"/>
       <c r="L21" s="25"/>
       <c r="M21" s="26"/>
     </row>
-    <row r="22" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
       <c r="M22" s="26"/>
     </row>
-    <row r="23" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
       <c r="K23" s="25"/>
       <c r="L23" s="25"/>
       <c r="M23" s="26"/>
     </row>
-    <row r="24" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="25"/>
       <c r="H24" s="25"/>
       <c r="K24" s="25"/>
       <c r="L24" s="25"/>
       <c r="M24" s="26"/>
     </row>
-    <row r="25" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="K25" s="25"/>
       <c r="L25" s="25"/>
       <c r="M25" s="26"/>
     </row>
-    <row r="26" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="K26" s="25"/>
       <c r="L26" s="25"/>
       <c r="M26" s="26"/>
     </row>
-    <row r="27" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="25"/>
       <c r="H27" s="25"/>
       <c r="K27" s="25"/>
       <c r="L27" s="25"/>
       <c r="M27" s="26"/>
     </row>
-    <row r="28" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
       <c r="K28" s="25"/>
       <c r="L28" s="25"/>
       <c r="M28" s="26"/>
     </row>
-    <row r="29" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="25"/>
       <c r="H29" s="25"/>
       <c r="K29" s="25"/>
       <c r="L29" s="25"/>
       <c r="M29" s="26"/>
     </row>
-    <row r="30" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="25"/>
       <c r="H30" s="25"/>
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
       <c r="M30" s="26"/>
     </row>
-    <row r="31" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="25"/>
       <c r="H31" s="25"/>
       <c r="K31" s="25"/>
       <c r="L31" s="25"/>
       <c r="M31" s="26"/>
     </row>
-    <row r="32" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="25"/>
       <c r="H32" s="25"/>
       <c r="K32" s="25"/>
@@ -2250,17 +2379,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -2275,11 +2405,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
@@ -2348,7 +2478,7 @@
       <c r="K6" s="25"/>
       <c r="L6" s="25"/>
     </row>
-    <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="35"/>
       <c r="C7" s="28" t="s">
         <v>112</v>
@@ -2361,10 +2491,19 @@
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="25"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>140</v>
+      </c>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
       <c r="I8" s="26"/>
@@ -2373,9 +2512,14 @@
       <c r="L8" s="25"/>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="44"/>
+      <c r="E9" s="36"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
       <c r="I9" s="26"/>
@@ -2384,9 +2528,10 @@
       <c r="L9" s="25"/>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="25"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
       <c r="I10" s="26"/>
@@ -2397,7 +2542,8 @@
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
-      <c r="D11" s="25"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
       <c r="I11" s="26"/>
@@ -2406,9 +2552,10 @@
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="25"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
       <c r="I12" s="26"/>
@@ -2417,9 +2564,10 @@
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="25"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
       <c r="I13" s="26"/>
@@ -2430,7 +2578,8 @@
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
-      <c r="D14" s="25"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
       <c r="I14" s="26"/>
@@ -2439,9 +2588,10 @@
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="25"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="I15" s="26"/>
@@ -2450,9 +2600,10 @@
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="25"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
       <c r="I16" s="26"/>
@@ -2460,7 +2611,11 @@
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
       <c r="I17" s="26"/>
@@ -2468,7 +2623,11 @@
       <c r="K17" s="25"/>
       <c r="L17" s="25"/>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="I18" s="26"/>
@@ -2476,7 +2635,11 @@
       <c r="K18" s="25"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
       <c r="I19" s="26"/>
@@ -2484,7 +2647,11 @@
       <c r="K19" s="25"/>
       <c r="L19" s="25"/>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="25"/>
       <c r="H20" s="25"/>
       <c r="I20" s="26"/>
@@ -2492,7 +2659,11 @@
       <c r="K20" s="25"/>
       <c r="L20" s="25"/>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
       <c r="I21" s="26"/>
@@ -2500,7 +2671,7 @@
       <c r="K21" s="25"/>
       <c r="L21" s="25"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="I22" s="26"/>
@@ -2508,7 +2679,7 @@
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
       <c r="I23" s="26"/>
@@ -2516,7 +2687,7 @@
       <c r="K23" s="25"/>
       <c r="L23" s="25"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="25"/>
       <c r="H24" s="25"/>
       <c r="I24" s="26"/>
@@ -2524,7 +2695,7 @@
       <c r="K24" s="25"/>
       <c r="L24" s="25"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="26"/>
@@ -2532,7 +2703,7 @@
       <c r="K25" s="25"/>
       <c r="L25" s="25"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="26"/>
@@ -2540,7 +2711,7 @@
       <c r="K26" s="25"/>
       <c r="L26" s="25"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="25"/>
       <c r="H27" s="25"/>
       <c r="I27" s="26"/>
@@ -2548,7 +2719,7 @@
       <c r="K27" s="25"/>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
       <c r="I28" s="26"/>
@@ -2556,7 +2727,7 @@
       <c r="K28" s="25"/>
       <c r="L28" s="25"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="25"/>
       <c r="H29" s="25"/>
       <c r="I29" s="26"/>
@@ -2564,7 +2735,7 @@
       <c r="K29" s="25"/>
       <c r="L29" s="25"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="25"/>
       <c r="H30" s="25"/>
       <c r="I30" s="26"/>
@@ -2572,7 +2743,7 @@
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="25"/>
       <c r="H31" s="25"/>
       <c r="I31" s="26"/>
@@ -2580,7 +2751,7 @@
       <c r="K31" s="25"/>
       <c r="L31" s="25"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="25"/>
       <c r="H32" s="25"/>
       <c r="I32" s="26"/>
@@ -2669,17 +2840,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -2694,11 +2866,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="28" t="s">
         <v>73</v>
       </c>
@@ -2739,7 +2911,7 @@
         <v>111</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G5" s="25"/>
       <c r="H5" s="25"/>
@@ -2761,7 +2933,7 @@
       <c r="K6" s="25"/>
       <c r="L6" s="25"/>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="35"/>
       <c r="C7" s="35"/>
       <c r="D7" s="25"/>
@@ -2772,10 +2944,19 @@
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="25"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>140</v>
+      </c>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
       <c r="I8" s="26"/>
@@ -2784,9 +2965,14 @@
       <c r="L8" s="25"/>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
       <c r="I9" s="26"/>
@@ -2795,9 +2981,10 @@
       <c r="L9" s="25"/>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="25"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
       <c r="I10" s="26"/>
@@ -2808,7 +2995,8 @@
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
-      <c r="D11" s="25"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
       <c r="I11" s="26"/>
@@ -2817,9 +3005,10 @@
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="25"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
       <c r="I12" s="26"/>
@@ -2828,9 +3017,10 @@
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="25"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
       <c r="I13" s="26"/>
@@ -2841,7 +3031,8 @@
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
-      <c r="D14" s="25"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
       <c r="I14" s="26"/>
@@ -2850,9 +3041,10 @@
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="25"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="I15" s="26"/>
@@ -2861,9 +3053,10 @@
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="25"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
       <c r="I16" s="26"/>
@@ -2871,7 +3064,11 @@
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
       <c r="I17" s="26"/>
@@ -2879,7 +3076,11 @@
       <c r="K17" s="25"/>
       <c r="L17" s="25"/>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="I18" s="26"/>
@@ -2887,7 +3088,11 @@
       <c r="K18" s="25"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
       <c r="I19" s="26"/>
@@ -2895,7 +3100,11 @@
       <c r="K19" s="25"/>
       <c r="L19" s="25"/>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="25"/>
       <c r="H20" s="25"/>
       <c r="I20" s="26"/>
@@ -2903,7 +3112,11 @@
       <c r="K20" s="25"/>
       <c r="L20" s="25"/>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
       <c r="I21" s="26"/>
@@ -2911,7 +3124,7 @@
       <c r="K21" s="25"/>
       <c r="L21" s="25"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="I22" s="26"/>
@@ -2919,7 +3132,7 @@
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
       <c r="I23" s="26"/>
@@ -2927,7 +3140,7 @@
       <c r="K23" s="25"/>
       <c r="L23" s="25"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="25"/>
       <c r="H24" s="25"/>
       <c r="I24" s="26"/>
@@ -2935,7 +3148,7 @@
       <c r="K24" s="25"/>
       <c r="L24" s="25"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="26"/>
@@ -2943,7 +3156,7 @@
       <c r="K25" s="25"/>
       <c r="L25" s="25"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="26"/>
@@ -2951,7 +3164,7 @@
       <c r="K26" s="25"/>
       <c r="L26" s="25"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="25"/>
       <c r="H27" s="25"/>
       <c r="I27" s="26"/>
@@ -2959,7 +3172,7 @@
       <c r="K27" s="25"/>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
       <c r="I28" s="26"/>
@@ -2967,7 +3180,7 @@
       <c r="K28" s="25"/>
       <c r="L28" s="25"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="25"/>
       <c r="H29" s="25"/>
       <c r="I29" s="26"/>
@@ -2975,7 +3188,7 @@
       <c r="K29" s="25"/>
       <c r="L29" s="25"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="25"/>
       <c r="H30" s="25"/>
       <c r="I30" s="26"/>
@@ -2983,7 +3196,7 @@
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="25"/>
       <c r="H31" s="25"/>
       <c r="I31" s="26"/>
@@ -2991,7 +3204,7 @@
       <c r="K31" s="25"/>
       <c r="L31" s="25"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="25"/>
       <c r="H32" s="25"/>
       <c r="I32" s="26"/>
@@ -3080,17 +3293,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -3105,11 +3319,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="B3" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
@@ -3140,13 +3354,13 @@
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="28" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>75</v>
@@ -3159,10 +3373,10 @@
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B6" s="37" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D6" s="25"/>
       <c r="G6" s="9" t="s">
@@ -3176,10 +3390,10 @@
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B7" s="37" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D7" s="25"/>
       <c r="G7" s="17" t="s">
@@ -3193,10 +3407,10 @@
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B8" s="37" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D8" s="25"/>
       <c r="G8" s="27" t="s">
@@ -3210,10 +3424,10 @@
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B9" s="16" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D9" s="25"/>
       <c r="G9" s="25"/>
@@ -3223,10 +3437,10 @@
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D10" s="25"/>
       <c r="G10" s="25"/>
@@ -3237,7 +3451,7 @@
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="36"/>
       <c r="C11" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D11" s="25"/>
       <c r="G11" s="25"/>
@@ -3245,7 +3459,7 @@
       <c r="K11" s="25"/>
       <c r="L11" s="25"/>
     </row>
-    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="35"/>
       <c r="D12" s="25"/>
       <c r="G12" s="25"/>
@@ -3253,132 +3467,195 @@
       <c r="K12" s="25"/>
       <c r="L12" s="25"/>
     </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="35"/>
-      <c r="D13" s="25"/>
+    <row r="13" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>140</v>
+      </c>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
       <c r="K13" s="25"/>
       <c r="L13" s="25"/>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="25"/>
+      <c r="B14" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
       <c r="K14" s="25"/>
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="25"/>
+      <c r="B15" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="K15" s="25"/>
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="25"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
       <c r="K17" s="25"/>
       <c r="L17" s="25"/>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="K18" s="25"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
       <c r="K19" s="25"/>
       <c r="L19" s="25"/>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="25"/>
       <c r="H20" s="25"/>
       <c r="K20" s="25"/>
       <c r="L20" s="25"/>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
       <c r="K21" s="25"/>
       <c r="L21" s="25"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
       <c r="K23" s="25"/>
       <c r="L23" s="25"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
       <c r="G24" s="25"/>
       <c r="H24" s="25"/>
       <c r="K24" s="25"/>
       <c r="L24" s="25"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="K25" s="25"/>
       <c r="L25" s="25"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="K26" s="25"/>
       <c r="L26" s="25"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="25"/>
       <c r="H27" s="25"/>
       <c r="K27" s="25"/>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
       <c r="K28" s="25"/>
       <c r="L28" s="25"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="25"/>
       <c r="H29" s="25"/>
       <c r="K29" s="25"/>
       <c r="L29" s="25"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="25"/>
       <c r="H30" s="25"/>
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="25"/>
       <c r="H31" s="25"/>
       <c r="K31" s="25"/>
       <c r="L31" s="25"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="25"/>
       <c r="H32" s="25"/>
       <c r="K32" s="25"/>
@@ -3455,17 +3732,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -3480,11 +3758,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="B3" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
@@ -3523,13 +3801,13 @@
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="28" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>79</v>
@@ -3583,7 +3861,7 @@
       <c r="K8" s="25"/>
       <c r="L8" s="25"/>
     </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="35"/>
       <c r="C9" s="35"/>
       <c r="D9" s="25"/>
@@ -3592,37 +3870,55 @@
       <c r="K9" s="25"/>
       <c r="L9" s="25"/>
     </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="25"/>
+    <row r="10" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>140</v>
+      </c>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
       <c r="K10" s="25"/>
       <c r="L10" s="25"/>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="25"/>
+      <c r="B11" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
       <c r="K11" s="25"/>
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="25"/>
+      <c r="B12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
       <c r="K12" s="25"/>
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="25"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
       <c r="K13" s="25"/>
@@ -3631,121 +3927,152 @@
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
-      <c r="D14" s="25"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
       <c r="K14" s="25"/>
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="25"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="K15" s="25"/>
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="25"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
       <c r="K17" s="25"/>
       <c r="L17" s="25"/>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="K18" s="25"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
       <c r="K19" s="25"/>
       <c r="L19" s="25"/>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="25"/>
       <c r="H20" s="25"/>
       <c r="K20" s="25"/>
       <c r="L20" s="25"/>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
       <c r="K21" s="25"/>
       <c r="L21" s="25"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
       <c r="K23" s="25"/>
       <c r="L23" s="25"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="25"/>
       <c r="H24" s="25"/>
       <c r="K24" s="25"/>
       <c r="L24" s="25"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="K25" s="25"/>
       <c r="L25" s="25"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="K26" s="25"/>
       <c r="L26" s="25"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="25"/>
       <c r="H27" s="25"/>
       <c r="K27" s="25"/>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
       <c r="K28" s="25"/>
       <c r="L28" s="25"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="25"/>
       <c r="H29" s="25"/>
       <c r="K29" s="25"/>
       <c r="L29" s="25"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="25"/>
       <c r="H30" s="25"/>
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="25"/>
       <c r="H31" s="25"/>
       <c r="K31" s="25"/>
       <c r="L31" s="25"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="25"/>
       <c r="H32" s="25"/>
       <c r="K32" s="25"/>
@@ -3822,17 +4149,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -3847,11 +4175,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="B3" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
@@ -3890,13 +4218,13 @@
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="28" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>75</v>
@@ -3914,7 +4242,7 @@
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B6" s="35"/>
       <c r="C6" s="28" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D6" s="25"/>
       <c r="G6" s="9" t="s">
@@ -3981,7 +4309,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="35"/>
       <c r="C10" s="35"/>
       <c r="D10" s="25"/>
@@ -3998,10 +4326,19 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="25"/>
+    <row r="11" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>140</v>
+      </c>
       <c r="G11" s="17" t="s">
         <v>77</v>
       </c>
@@ -4016,9 +4353,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="25"/>
+      <c r="B12" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
       <c r="K12" s="17" t="s">
@@ -4029,9 +4371,14 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="25"/>
+      <c r="B13" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
       <c r="K13" s="24" t="s">
@@ -4042,123 +4389,174 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="25"/>
+      <c r="B14" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
       <c r="K14" s="21"/>
       <c r="L14" s="21"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="25"/>
+      <c r="B15" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="K15" s="25"/>
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="25"/>
+      <c r="B16" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="36"/>
+      <c r="C17" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
       <c r="K17" s="25"/>
       <c r="L17" s="25"/>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="K18" s="25"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
       <c r="K19" s="25"/>
       <c r="L19" s="25"/>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="25"/>
       <c r="H20" s="25"/>
       <c r="K20" s="25"/>
       <c r="L20" s="25"/>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
       <c r="K21" s="25"/>
       <c r="L21" s="25"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
       <c r="K23" s="25"/>
       <c r="L23" s="25"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
       <c r="G24" s="25"/>
       <c r="H24" s="25"/>
       <c r="K24" s="25"/>
       <c r="L24" s="25"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="K25" s="25"/>
       <c r="L25" s="25"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="K26" s="25"/>
       <c r="L26" s="25"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="25"/>
       <c r="H27" s="25"/>
       <c r="K27" s="25"/>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
       <c r="K28" s="25"/>
       <c r="L28" s="25"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="25"/>
       <c r="H29" s="25"/>
       <c r="K29" s="25"/>
       <c r="L29" s="25"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="25"/>
       <c r="H30" s="25"/>
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="25"/>
       <c r="H31" s="25"/>
       <c r="K31" s="25"/>
       <c r="L31" s="25"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="25"/>
       <c r="H32" s="25"/>
       <c r="K32" s="25"/>
@@ -4235,17 +4633,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -4260,11 +4659,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
+      <c r="B3" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="18" t="s">
         <v>100</v>
       </c>
@@ -4303,13 +4702,13 @@
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="28" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="G5" s="18" t="s">
         <v>102</v>
@@ -4382,7 +4781,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="35"/>
       <c r="C10" s="35"/>
       <c r="D10" s="25"/>
@@ -4395,10 +4794,19 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="25"/>
+    <row r="11" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>140</v>
+      </c>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
       <c r="K11" s="17" t="s">
@@ -4409,9 +4817,16 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="25"/>
+      <c r="B12" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" s="36"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
       <c r="K12" s="17" t="s">
@@ -4422,9 +4837,16 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="25"/>
+      <c r="B13" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" s="36"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
       <c r="K13" s="18" t="s">
@@ -4435,9 +4857,16 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="25"/>
+      <c r="B14" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" s="36"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
       <c r="K14" s="17" t="s">
@@ -4448,9 +4877,16 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="25"/>
+      <c r="B15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="36"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="K15" s="17" t="s">
@@ -4461,9 +4897,14 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="25"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" s="36"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
       <c r="K16" s="17" t="s">
@@ -4473,7 +4914,13 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="36"/>
+      <c r="C17" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
       <c r="K17" s="17" t="s">
@@ -4483,7 +4930,13 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="K18" s="18" t="s">
@@ -4493,7 +4946,13 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
       <c r="K19" s="18" t="s">
@@ -4503,7 +4962,13 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="36"/>
+      <c r="C20" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="25"/>
       <c r="H20" s="25"/>
       <c r="K20" s="32" t="s">
@@ -4513,73 +4978,89 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
       <c r="K21" s="21"/>
       <c r="L21" s="21"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
       <c r="K23" s="25"/>
       <c r="L23" s="25"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
       <c r="G24" s="25"/>
       <c r="H24" s="25"/>
       <c r="K24" s="25"/>
       <c r="L24" s="25"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="K25" s="25"/>
       <c r="L25" s="25"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="K26" s="25"/>
       <c r="L26" s="25"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="25"/>
       <c r="H27" s="25"/>
       <c r="K27" s="25"/>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
       <c r="K28" s="25"/>
       <c r="L28" s="25"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="25"/>
       <c r="H29" s="25"/>
       <c r="K29" s="25"/>
       <c r="L29" s="25"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="25"/>
       <c r="H30" s="25"/>
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="25"/>
       <c r="H31" s="25"/>
       <c r="K31" s="25"/>
       <c r="L31" s="25"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="25"/>
       <c r="H32" s="25"/>
       <c r="K32" s="25"/>
